--- a/example_files/dump_of_all_notes.xlsx
+++ b/example_files/dump_of_all_notes.xlsx
@@ -44,16 +44,16 @@
     <t>SecondExam</t>
   </si>
   <si>
-    <t>albert.enstn</t>
-  </si>
-  <si>
-    <t>gabriel.crmr</t>
-  </si>
-  <si>
-    <t>marie.cr</t>
-  </si>
-  <si>
-    <t>richard.fynmn</t>
+    <t>EINSTEIN Albert</t>
+  </si>
+  <si>
+    <t>CRAMER Gabriel</t>
+  </si>
+  <si>
+    <t>CURIE Marie</t>
+  </si>
+  <si>
+    <t>FEYNMANN Richard</t>
   </si>
   <si>
     <t>NIP</t>
@@ -77,73 +77,73 @@
     <t>Orals</t>
   </si>
   <si>
-    <t>isabella.prz</t>
-  </si>
-  <si>
-    <t>william.km</t>
-  </si>
-  <si>
-    <t>sophia.l</t>
-  </si>
-  <si>
-    <t>ethan.mrtnz</t>
-  </si>
-  <si>
-    <t>madison.rvr</t>
-  </si>
-  <si>
-    <t>jacob.mtchll</t>
-  </si>
-  <si>
-    <t>emily.hrnndz</t>
-  </si>
-  <si>
-    <t>michael.dvs</t>
-  </si>
-  <si>
-    <t>mia.cpr</t>
-  </si>
-  <si>
-    <t>alexander.jcksn</t>
-  </si>
-  <si>
-    <t>ava.rmrz</t>
-  </si>
-  <si>
-    <t>benjamin.grn</t>
-  </si>
-  <si>
-    <t>olivia.smth</t>
-  </si>
-  <si>
-    <t>elijah.jhnsn</t>
-  </si>
-  <si>
-    <t>charlotte.wlsn</t>
-  </si>
-  <si>
-    <t>lucas.brwn</t>
-  </si>
-  <si>
-    <t>emma.trnr</t>
-  </si>
-  <si>
-    <t>jayden.adms</t>
-  </si>
-  <si>
-    <t>abigail.thms</t>
-  </si>
-  <si>
-    <t>daniel.tylr</t>
-  </si>
-  <si>
-    <t>grace.crtr</t>
-  </si>
-  <si>
-    <t>christopher.l</t>
-  </si>
-  <si>
-    <t>victoria.gnzlz</t>
+    <t>PEREZ Isabella</t>
+  </si>
+  <si>
+    <t>KIM William</t>
+  </si>
+  <si>
+    <t>LEE Sophia</t>
+  </si>
+  <si>
+    <t>MARTINEZ Ethan</t>
+  </si>
+  <si>
+    <t>RIVERA Madison</t>
+  </si>
+  <si>
+    <t>MITCHELL Jacob</t>
+  </si>
+  <si>
+    <t>HERNANDEZ Emily</t>
+  </si>
+  <si>
+    <t>DAVIS Michael</t>
+  </si>
+  <si>
+    <t>COOPER Mia</t>
+  </si>
+  <si>
+    <t>JACKSON Alexander</t>
+  </si>
+  <si>
+    <t>RAMIREZ Ava</t>
+  </si>
+  <si>
+    <t>GREEN Benjamin</t>
+  </si>
+  <si>
+    <t>SMITH Olivia</t>
+  </si>
+  <si>
+    <t>JOHNSON Elijah</t>
+  </si>
+  <si>
+    <t>WILSON Charlotte</t>
+  </si>
+  <si>
+    <t>BROWN Lucas</t>
+  </si>
+  <si>
+    <t>TURNER Emma</t>
+  </si>
+  <si>
+    <t>ADAMS Jayden</t>
+  </si>
+  <si>
+    <t>THOMAS Abigail</t>
+  </si>
+  <si>
+    <t>TAYLOR Daniel</t>
+  </si>
+  <si>
+    <t>CARTER Grace</t>
+  </si>
+  <si>
+    <t>LEE Christopher</t>
+  </si>
+  <si>
+    <t>GONZALEZ Victoria</t>
   </si>
 </sst>
 </file>
